--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jul-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jul-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1820</v>
+        <v>79843.36</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>731.5287</v>
+        <v>32092.15</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>38530.665</v>
+        <v>1690339.34</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>10270.8</v>
+        <v>450579.75</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>752.64</v>
+        <v>33018.3</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>232.407</v>
+        <v>10195.69</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>675.3474</v>
+        <v>29627.47</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3011.281</v>
+        <v>132104.82</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>502.2</v>
+        <v>22031.5</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>175.3478</v>
+        <v>7692.5</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>360.2382</v>
+        <v>15803.64</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1104</v>
+        <v>48432.45</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>828</v>
+        <v>36324.34</v>
       </c>
     </row>
     <row r="15">
@@ -1358,11 +1358,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>558</v>
+        <v>24479.45</v>
       </c>
     </row>
     <row r="16">
@@ -1419,11 +1419,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1737.88</v>
+        <v>76240.75</v>
       </c>
     </row>
     <row r="17">
@@ -1480,11 +1480,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>297.6</v>
+        <v>13055.7</v>
       </c>
     </row>
     <row r="18">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>388</v>
+        <v>17021.55</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>608.6849999999999</v>
+        <v>26703</v>
       </c>
     </row>
     <row r="20">
@@ -1663,11 +1663,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>10965.0425</v>
+        <v>481036.15</v>
       </c>
     </row>
     <row r="21">
@@ -1724,11 +1724,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1251.2</v>
+        <v>54890.11</v>
       </c>
     </row>
     <row r="22">
@@ -1785,11 +1785,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>203.763</v>
+        <v>8939.08</v>
       </c>
     </row>
     <row r="23">
@@ -1846,11 +1846,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>418.5</v>
+        <v>18359.58</v>
       </c>
     </row>
     <row r="24">
@@ -1907,11 +1907,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>853.3056</v>
+        <v>37434.5</v>
       </c>
     </row>
     <row r="25">
@@ -1968,11 +1968,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>873.6</v>
+        <v>38324.81</v>
       </c>
     </row>
     <row r="26">
@@ -2029,11 +2029,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1196</v>
+        <v>52468.49</v>
       </c>
     </row>
     <row r="27">
@@ -2090,11 +2090,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>692.58</v>
+        <v>30383.47</v>
       </c>
     </row>
     <row r="28">
@@ -2151,11 +2151,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>459.816</v>
+        <v>20172.12</v>
       </c>
     </row>
     <row r="29">
@@ -2212,11 +2212,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>394.1266</v>
+        <v>17290.32</v>
       </c>
     </row>
     <row r="30">
@@ -2273,11 +2273,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>170.19</v>
+        <v>7466.23</v>
       </c>
     </row>
     <row r="31">
@@ -2334,17 +2334,17 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>851.2</v>
+        <v>37342.12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1499-2468-CM26</t>
+          <t>4343-131-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2369,43 +2369,43 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.608.402-k</t>
+          <t>61.606.912-8</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DEL TORAX</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>LAHUEN HEALTH SERVICES SPA</t>
+          <t>GEORG</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.227.643-7</t>
+          <t>76.624.276-6</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>361.584</v>
+        <v>7209.65</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4343-131-CM26</t>
+          <t>1499-2468-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2430,37 +2430,37 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.606.912-8</t>
+          <t>61.608.402-k</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
+          <t>INSTITUTO NACIONAL DEL TORAX</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>LAHUEN HEALTH SERVICES SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
+          <t>76.227.643-7</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>164.3414</v>
+        <v>15862.68</v>
       </c>
     </row>
     <row r="34">
@@ -2517,11 +2517,11 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>958.3456</v>
+        <v>42042.6</v>
       </c>
     </row>
     <row r="35">
@@ -2578,11 +2578,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>319.8363</v>
+        <v>14031.21</v>
       </c>
     </row>
     <row r="36">
@@ -2639,11 +2639,11 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>20853.576</v>
+        <v>914845.87</v>
       </c>
     </row>
     <row r="37">
@@ -2700,11 +2700,11 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>186</v>
+        <v>8159.82</v>
       </c>
     </row>
     <row r="38">
@@ -2761,11 +2761,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>741.489</v>
+        <v>32529.1</v>
       </c>
     </row>
     <row r="39">
@@ -2822,11 +2822,11 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>165.54</v>
+        <v>7262.24</v>
       </c>
     </row>
     <row r="40">
@@ -2883,11 +2883,11 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1094.8</v>
+        <v>48028.85</v>
       </c>
     </row>
     <row r="41">
@@ -2944,11 +2944,11 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>188.0367</v>
+        <v>8249.17</v>
       </c>
     </row>
     <row r="42">
@@ -3005,11 +3005,11 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>359.8952</v>
+        <v>15788.59</v>
       </c>
     </row>
     <row r="43">
@@ -3066,17 +3066,17 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1590.0046</v>
+        <v>69753.46000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2702-358-CM26</t>
+          <t>924-242-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,28 +3116,28 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>230.3</v>
+        <v>46263.52</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>924-242-CM26</t>
+          <t>2702-358-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,22 +3177,22 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1054.56</v>
+        <v>10103.26</v>
       </c>
     </row>
     <row r="46">
@@ -3249,11 +3249,11 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2250</v>
+        <v>98707.45</v>
       </c>
     </row>
     <row r="47">
@@ -3310,11 +3310,11 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>242.5</v>
+        <v>10638.47</v>
       </c>
     </row>
     <row r="48">
@@ -3371,11 +3371,11 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1806.5593</v>
+        <v>79253.71000000001</v>
       </c>
     </row>
     <row r="49">
@@ -3432,11 +3432,11 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1159.2</v>
+        <v>50854.08</v>
       </c>
     </row>
     <row r="50">
@@ -3493,17 +3493,17 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>359.91</v>
+        <v>15789.24</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2455-107-CM26</t>
+          <t>4666-1-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.071.000-5</t>
+          <t>60.901.000-2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUINTA NORMAL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,28 +3543,28 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>USERCODE SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>77.347.464-8</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>5970.51</v>
+        <v>21540.28</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>711841-231-SE26</t>
+          <t>2455-107-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>69.071.000-5</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUINTA NORMAL</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,32 +3604,28 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ALTAVOZ SOCIEDAD ANONIMA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>96.827.350-7</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>240.028593</v>
+        <v>261926.13</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>869591-36-CM26</t>
+          <t>711841-231-SE26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3654,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>60.808.000-7</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3669,28 +3665,32 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>XMS Business Solutions S.A.</t>
+          <t>ALTAVOZ SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.249.938-k</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>96.827.350-7</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1045.7958</v>
+        <v>10530.05</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>711841-243-SE26</t>
+          <t>869591-36-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>60.808.000-7</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3730,32 +3730,28 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ANTICIPA S A</t>
+          <t>XMS Business Solutions S.A.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.771.610-3</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.249.938-k</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>398.002521</v>
+        <v>45879.04</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>711841-246-SE26</t>
+          <t>711841-243-SE26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3775,7 +3771,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Enviada a Proveedor</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3795,12 +3791,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>ANTICIPA S A</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
+          <t>96.771.610-3</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3810,17 +3806,17 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1188.2528344</v>
+        <v>17460.36</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>4666-1-CM26</t>
+          <t>1147293-198-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3845,12 +3841,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>60.901.000-2</t>
+          <t>70.930.000-8</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>Fundación para la Innovación Agraria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3860,28 +3856,28 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>USERCODE SPA</t>
+          <t>NEWTENBERG PUBLICACIONES DIGITALES LIMITADA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>77.347.464-8</t>
+          <t>77.543.180-6</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>491.0028</v>
+        <v>17390.62</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1147293-198-CM26</t>
+          <t>1549-3396-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3896,7 +3892,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3906,12 +3902,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>70.930.000-8</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fundación para la Innovación Agraria</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3921,28 +3917,28 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>NEWTENBERG PUBLICACIONES DIGITALES LIMITADA</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>77.543.180-6</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>396.4128</v>
+        <v>12085.64</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1549-3396-CM26</t>
+          <t>721703-316-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3967,12 +3963,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.980.230-6</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>AGENCIA DE CALIDAD DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3982,28 +3978,28 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
+          <t>76.891.821-k</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>275.4878</v>
+        <v>19991.55</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>721703-316-CM26</t>
+          <t>606-299-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4028,12 +4024,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.980.230-6</t>
+          <t>60.513.000-3</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>AGENCIA DE CALIDAD DE LA EDUCACION</t>
+          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4043,83 +4039,22 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>Pragma Informatica S.A.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>455.7</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>606-299-CM26</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>60.513.000-3</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Pragma Informatica S.A.</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>77.063.770-8</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>CLF</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="n">
-        <v>3071.8586</v>
+        <v>134762.36</v>
       </c>
     </row>
   </sheetData>
